--- a/Data/4DataSet_VLM-DTI.xlsx
+++ b/Data/4DataSet_VLM-DTI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\survey-outer\第二篇开头\论文2\数据整理\OT_QCM2Net\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niu\Documents\Codex\2026-07-14\7-30-slack-plugin-slack-openai-4\outputs\VLM_DTI_FinalProvenance_20260723\VLM-DTI source code\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6990170-752E-4299-B073-A652A92489B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887991C-7735-40F6-963E-DEA2865581CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="1335" windowWidth="16350" windowHeight="12420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7740" yWindow="450" windowWidth="16350" windowHeight="14415" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="celegans" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="19">
   <si>
     <t>Dataset</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Seed</t>
-  </si>
-  <si>
-    <t>BestEpoch</t>
   </si>
   <si>
     <t>AUC_Test</t>
@@ -1486,13 +1483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,1047 +1520,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>14</v>
+        <v>0.99319999999999997</v>
       </c>
       <c r="E2" s="4">
-        <v>0.99319999999999997</v>
+        <v>0.99329999999999996</v>
       </c>
       <c r="F2" s="4">
         <v>0.99329999999999996</v>
       </c>
       <c r="G2" s="4">
-        <v>0.99329999999999996</v>
+        <v>0.94359999999999999</v>
       </c>
       <c r="H2" s="4">
-        <v>0.94359999999999999</v>
+        <v>0.98129999999999995</v>
       </c>
       <c r="I2" s="4">
-        <v>0.98129999999999995</v>
+        <v>0.96279999999999999</v>
       </c>
       <c r="J2" s="4">
-        <v>0.96279999999999999</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.96209999999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>11</v>
+        <v>0.99370000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>0.99370000000000003</v>
+        <v>0.99309999999999998</v>
       </c>
       <c r="F3" s="4">
         <v>0.99309999999999998</v>
       </c>
       <c r="G3" s="4">
-        <v>0.99309999999999998</v>
+        <v>0.95489999999999997</v>
       </c>
       <c r="H3" s="4">
-        <v>0.95489999999999997</v>
+        <v>0.96</v>
       </c>
       <c r="I3" s="4">
-        <v>0.96</v>
+        <v>0.95889999999999997</v>
       </c>
       <c r="J3" s="4">
-        <v>0.95889999999999997</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.95740000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>25</v>
+        <v>0.99450000000000005</v>
       </c>
       <c r="E4" s="4">
-        <v>0.99450000000000005</v>
+        <v>0.99409999999999998</v>
       </c>
       <c r="F4" s="4">
         <v>0.99409999999999998</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99409999999999998</v>
+        <v>0.95809999999999995</v>
       </c>
       <c r="H4" s="4">
-        <v>0.95809999999999995</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="I4" s="4">
-        <v>0.97599999999999998</v>
+        <v>0.96789999999999998</v>
       </c>
       <c r="J4" s="4">
-        <v>0.96789999999999998</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.96699999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>29</v>
+        <v>0.99480000000000002</v>
       </c>
       <c r="E5" s="4">
-        <v>0.99480000000000002</v>
+        <v>0.99439999999999995</v>
       </c>
       <c r="F5" s="4">
         <v>0.99439999999999995</v>
       </c>
       <c r="G5" s="4">
-        <v>0.99439999999999995</v>
+        <v>0.96809999999999996</v>
       </c>
       <c r="H5" s="4">
-        <v>0.96809999999999996</v>
+        <v>0.97070000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.97070000000000001</v>
+        <v>0.97050000000000003</v>
       </c>
       <c r="J5" s="4">
-        <v>0.97050000000000003</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.96940000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>27</v>
+        <v>0.99429999999999996</v>
       </c>
       <c r="E6" s="4">
-        <v>0.99429999999999996</v>
+        <v>0.99450000000000005</v>
       </c>
       <c r="F6" s="4">
         <v>0.99450000000000005</v>
       </c>
       <c r="G6" s="4">
-        <v>0.99450000000000005</v>
+        <v>0.96540000000000004</v>
       </c>
       <c r="H6" s="4">
-        <v>0.96540000000000004</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="I6" s="4">
-        <v>0.96799999999999997</v>
+        <v>0.96789999999999998</v>
       </c>
       <c r="J6" s="4">
-        <v>0.96789999999999998</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.9667</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9941±0.0006</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9941±0.0006</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9939±0.0006</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9939±0.0006</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9939±0.0006</v>
+        <v>0.9580±0.0097</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9580±0.0097</v>
+        <v>0.9712±0.0081</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9712±0.0081</v>
+        <v>0.9656±0.0047</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9656±0.0047</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9645±0.0048</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>13</v>
+        <v>0.94069999999999998</v>
       </c>
       <c r="E8" s="4">
-        <v>0.94069999999999998</v>
+        <v>0.92759999999999998</v>
       </c>
       <c r="F8" s="4">
-        <v>0.92759999999999998</v>
+        <v>0.92769999999999997</v>
       </c>
       <c r="G8" s="4">
-        <v>0.92769999999999997</v>
+        <v>0.81210000000000004</v>
       </c>
       <c r="H8" s="4">
-        <v>0.81210000000000004</v>
+        <v>0.87370000000000003</v>
       </c>
       <c r="I8" s="4">
-        <v>0.87370000000000003</v>
+        <v>0.86280000000000001</v>
       </c>
       <c r="J8" s="4">
-        <v>0.86280000000000001</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.84179999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>26</v>
+        <v>0.95989999999999998</v>
       </c>
       <c r="E9" s="4">
-        <v>0.95989999999999998</v>
+        <v>0.94840000000000002</v>
       </c>
       <c r="F9" s="4">
         <v>0.94840000000000002</v>
       </c>
       <c r="G9" s="4">
-        <v>0.94840000000000002</v>
+        <v>0.88390000000000002</v>
       </c>
       <c r="H9" s="4">
-        <v>0.88390000000000002</v>
+        <v>0.8337</v>
       </c>
       <c r="I9" s="4">
-        <v>0.8337</v>
+        <v>0.88480000000000003</v>
       </c>
       <c r="J9" s="4">
-        <v>0.88480000000000003</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.85809999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>25</v>
+        <v>0.95579999999999998</v>
       </c>
       <c r="E10" s="4">
-        <v>0.95579999999999998</v>
+        <v>0.94330000000000003</v>
       </c>
       <c r="F10" s="4">
-        <v>0.94330000000000003</v>
+        <v>0.94340000000000002</v>
       </c>
       <c r="G10" s="4">
-        <v>0.94340000000000002</v>
+        <v>0.86529999999999996</v>
       </c>
       <c r="H10" s="4">
         <v>0.86529999999999996</v>
       </c>
       <c r="I10" s="4">
+        <v>0.88739999999999997</v>
+      </c>
+      <c r="J10" s="4">
         <v>0.86529999999999996</v>
       </c>
-      <c r="J10" s="4">
-        <v>0.88739999999999997</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0.86529999999999996</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>30</v>
+        <v>0.95950000000000002</v>
       </c>
       <c r="E11" s="4">
-        <v>0.95950000000000002</v>
+        <v>0.94979999999999998</v>
       </c>
       <c r="F11" s="4">
-        <v>0.94979999999999998</v>
+        <v>0.94989999999999997</v>
       </c>
       <c r="G11" s="4">
-        <v>0.94989999999999997</v>
+        <v>0.86509999999999998</v>
       </c>
       <c r="H11" s="4">
-        <v>0.86509999999999998</v>
+        <v>0.87790000000000001</v>
       </c>
       <c r="I11" s="4">
-        <v>0.87790000000000001</v>
+        <v>0.89180000000000004</v>
       </c>
       <c r="J11" s="4">
-        <v>0.89180000000000004</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.87150000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>20</v>
+        <v>0.94730000000000003</v>
       </c>
       <c r="E12" s="4">
-        <v>0.94730000000000003</v>
+        <v>0.9284</v>
       </c>
       <c r="F12" s="4">
-        <v>0.9284</v>
+        <v>0.92849999999999999</v>
       </c>
       <c r="G12" s="4">
-        <v>0.92849999999999999</v>
+        <v>0.8599</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8599</v>
+        <v>0.84</v>
       </c>
       <c r="I12" s="4">
-        <v>0.84</v>
+        <v>0.876</v>
       </c>
       <c r="J12" s="4">
-        <v>0.876</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.8498</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9526±0.0084</v>
+      </c>
       <c r="E13" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9526±0.0084</v>
+        <f t="shared" ref="E13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
+        <v>0.9395±0.0108</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" ref="F13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(F8:F12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F8:F12),"0.0000")</f>
-        <v>0.9395±0.0108</v>
+        <f t="shared" si="1"/>
+        <v>0.9396±0.0108</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9396±0.0108</v>
+        <v>0.8573±0.0268</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8573±0.0268</v>
+        <v>0.8581±0.0201</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8581±0.0201</v>
+        <v>0.8806±0.0115</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8806±0.0115</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8573±0.0119</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>7</v>
+        <v>0.96419999999999995</v>
       </c>
       <c r="E14" s="4">
-        <v>0.96419999999999995</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="F14" s="4">
         <v>0.97399999999999998</v>
       </c>
       <c r="G14" s="4">
-        <v>0.97399999999999998</v>
+        <v>0.97909999999999997</v>
       </c>
       <c r="H14" s="4">
-        <v>0.97909999999999997</v>
+        <v>0.73980000000000001</v>
       </c>
       <c r="I14" s="4">
-        <v>0.73980000000000001</v>
+        <v>0.84240000000000004</v>
       </c>
       <c r="J14" s="4">
-        <v>0.84240000000000004</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.84279999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>6</v>
+        <v>0.97389999999999999</v>
       </c>
       <c r="E15" s="4">
-        <v>0.97389999999999999</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="F15" s="4">
         <v>0.97989999999999999</v>
       </c>
       <c r="G15" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.97109999999999996</v>
       </c>
       <c r="H15" s="4">
-        <v>0.97109999999999996</v>
+        <v>0.84389999999999998</v>
       </c>
       <c r="I15" s="4">
-        <v>0.84389999999999998</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="J15" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.90300000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>8</v>
+        <v>0.96430000000000005</v>
       </c>
       <c r="E16" s="4">
-        <v>0.96430000000000005</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="F16" s="4">
         <v>0.97299999999999998</v>
       </c>
       <c r="G16" s="4">
-        <v>0.97299999999999998</v>
+        <v>0.97209999999999996</v>
       </c>
       <c r="H16" s="4">
-        <v>0.97209999999999996</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="I16" s="4">
-        <v>0.77700000000000002</v>
+        <v>0.8599</v>
       </c>
       <c r="J16" s="4">
-        <v>0.8599</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.86360000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>10</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="E17" s="4">
-        <v>0.96579999999999999</v>
+        <v>0.97509999999999997</v>
       </c>
       <c r="F17" s="4">
         <v>0.97509999999999997</v>
       </c>
       <c r="G17" s="4">
-        <v>0.97509999999999997</v>
+        <v>0.97609999999999997</v>
       </c>
       <c r="H17" s="4">
-        <v>0.97609999999999997</v>
+        <v>0.76019999999999999</v>
       </c>
       <c r="I17" s="4">
-        <v>0.76019999999999999</v>
+        <v>0.85250000000000004</v>
       </c>
       <c r="J17" s="4">
-        <v>0.85250000000000004</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.85470000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>6</v>
+        <v>0.96960000000000002</v>
       </c>
       <c r="E18" s="4">
-        <v>0.96960000000000002</v>
+        <v>0.97619999999999996</v>
       </c>
       <c r="F18" s="4">
         <v>0.97619999999999996</v>
       </c>
       <c r="G18" s="4">
-        <v>0.97619999999999996</v>
+        <v>0.94720000000000004</v>
       </c>
       <c r="H18" s="4">
-        <v>0.94720000000000004</v>
+        <v>0.91639999999999999</v>
       </c>
       <c r="I18" s="4">
-        <v>0.91639999999999999</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="J18" s="4">
-        <v>0.92310000000000003</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.93149999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9676±0.0042</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9676±0.0042</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9756±0.0027</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
+        <f t="shared" si="2"/>
         <v>0.9756±0.0027</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9756±0.0027</v>
+        <v>0.9691±0.0127</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9691±0.0127</v>
+        <v>0.8075±0.0723</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8075±0.0723</v>
+        <v>0.8749±0.0338</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8749±0.0338</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.8791±0.0370</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>16</v>
+        <v>0.99539999999999995</v>
       </c>
       <c r="E20" s="4">
-        <v>0.99539999999999995</v>
+        <v>0.99580000000000002</v>
       </c>
       <c r="F20" s="4">
         <v>0.99580000000000002</v>
       </c>
       <c r="G20" s="4">
-        <v>0.99580000000000002</v>
+        <v>0.94079999999999997</v>
       </c>
       <c r="H20" s="4">
-        <v>0.94079999999999997</v>
+        <v>0.9597</v>
       </c>
       <c r="I20" s="4">
-        <v>0.9597</v>
+        <v>0.9486</v>
       </c>
       <c r="J20" s="4">
-        <v>0.9486</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.95020000000000004</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>25</v>
+        <v>0.99670000000000003</v>
       </c>
       <c r="E21" s="4">
-        <v>0.99670000000000003</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="F21" s="4">
-        <v>0.99680000000000002</v>
+        <v>0.99690000000000001</v>
       </c>
       <c r="G21" s="4">
-        <v>0.99690000000000001</v>
+        <v>0.95450000000000002</v>
       </c>
       <c r="H21" s="4">
-        <v>0.95450000000000002</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="I21" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.96919999999999995</v>
       </c>
       <c r="J21" s="4">
-        <v>0.96919999999999995</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.97030000000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>19</v>
+        <v>0.99570000000000003</v>
       </c>
       <c r="E22" s="4">
-        <v>0.99570000000000003</v>
+        <v>0.99590000000000001</v>
       </c>
       <c r="F22" s="4">
-        <v>0.99590000000000001</v>
+        <v>0.996</v>
       </c>
       <c r="G22" s="4">
-        <v>0.996</v>
+        <v>0.95420000000000005</v>
       </c>
       <c r="H22" s="4">
-        <v>0.95420000000000005</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I22" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="J22" s="4">
-        <v>0.96579999999999999</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.96689999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>24</v>
+        <v>0.99729999999999996</v>
       </c>
       <c r="E23" s="4">
-        <v>0.99729999999999996</v>
+        <v>0.99750000000000005</v>
       </c>
       <c r="F23" s="4">
-        <v>0.99750000000000005</v>
+        <v>0.99760000000000004</v>
       </c>
       <c r="G23" s="4">
-        <v>0.99760000000000004</v>
+        <v>0.96709999999999996</v>
       </c>
       <c r="H23" s="4">
-        <v>0.96709999999999996</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="I23" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J23" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.97670000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>26</v>
+        <v>0.99550000000000005</v>
       </c>
       <c r="E24" s="4">
-        <v>0.99550000000000005</v>
+        <v>0.99619999999999997</v>
       </c>
       <c r="F24" s="4">
         <v>0.99619999999999997</v>
       </c>
       <c r="G24" s="4">
-        <v>0.99619999999999997</v>
+        <v>0.94189999999999996</v>
       </c>
       <c r="H24" s="4">
-        <v>0.94189999999999996</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="I24" s="4">
-        <v>0.97989999999999999</v>
+        <v>0.95889999999999997</v>
       </c>
       <c r="J24" s="4">
-        <v>0.95889999999999997</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.96050000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9961±0.0008</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9961±0.0008</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9964±0.0007</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9964±0.0007</v>
+        <f t="shared" si="3"/>
+        <v>0.9965±0.0007</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9965±0.0007</v>
+        <v>0.9517±0.0108</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9517±0.0108</v>
+        <v>0.9785±0.0111</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9785±0.0111</v>
+        <v>0.9637±0.0105</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9637±0.0105</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9649±0.0101</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>20</v>
+        <v>0.999</v>
       </c>
       <c r="E26" s="4">
-        <v>0.999</v>
+        <v>0.99919999999999998</v>
       </c>
       <c r="F26" s="4">
         <v>0.99919999999999998</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99919999999999998</v>
+        <v>0.99280000000000002</v>
       </c>
       <c r="H26" s="4">
-        <v>0.99280000000000002</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="I26" s="4">
-        <v>0.98560000000000003</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="J26" s="4">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.98919999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>27</v>
+        <v>0.99790000000000001</v>
       </c>
       <c r="E27" s="4">
-        <v>0.99790000000000001</v>
+        <v>0.99819999999999998</v>
       </c>
       <c r="F27" s="4">
         <v>0.99819999999999998</v>
       </c>
       <c r="G27" s="4">
-        <v>0.99819999999999998</v>
+        <v>0.97840000000000005</v>
       </c>
       <c r="H27" s="4">
         <v>0.97840000000000005</v>
       </c>
       <c r="I27" s="4">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="J27" s="4">
         <v>0.97840000000000005</v>
       </c>
-      <c r="J27" s="4">
-        <v>0.97599999999999998</v>
-      </c>
-      <c r="K27" s="4">
-        <v>0.97840000000000005</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>28</v>
+        <v>0.99860000000000004</v>
       </c>
       <c r="E28" s="4">
-        <v>0.99860000000000004</v>
+        <v>0.99880000000000002</v>
       </c>
       <c r="F28" s="4">
         <v>0.99880000000000002</v>
       </c>
       <c r="G28" s="4">
-        <v>0.99880000000000002</v>
+        <v>0.99280000000000002</v>
       </c>
       <c r="H28" s="4">
-        <v>0.99280000000000002</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="I28" s="4">
-        <v>0.98560000000000003</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="J28" s="4">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.98919999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>25</v>
+        <v>0.99819999999999998</v>
       </c>
       <c r="E29" s="4">
-        <v>0.99819999999999998</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="F29" s="4">
         <v>0.99850000000000005</v>
       </c>
       <c r="G29" s="4">
-        <v>0.99850000000000005</v>
+        <v>0.99250000000000005</v>
       </c>
       <c r="H29" s="4">
-        <v>0.99250000000000005</v>
+        <v>0.9496</v>
       </c>
       <c r="I29" s="4">
-        <v>0.9496</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="J29" s="4">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.97060000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>24</v>
+        <v>0.99809999999999999</v>
       </c>
       <c r="E30" s="4">
-        <v>0.99809999999999999</v>
+        <v>0.99850000000000005</v>
       </c>
       <c r="F30" s="4">
         <v>0.99850000000000005</v>
       </c>
       <c r="G30" s="4">
-        <v>0.99850000000000005</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H30" s="4">
-        <v>0.99219999999999997</v>
+        <v>0.92090000000000005</v>
       </c>
       <c r="I30" s="4">
-        <v>0.92090000000000005</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="J30" s="4">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.95520000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9984±0.0004</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9984±0.0004</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9986±0.0004</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9986±0.0004</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9986±0.0004</v>
+        <v>0.9897±0.0063</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9897±0.0063</v>
+        <v>0.9640±0.0283</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9640±0.0283</v>
+        <v>0.9744±0.0151</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9744±0.0151</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9765±0.0143</v>
       </c>
@@ -2577,10 +2492,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FE8A1-466E-4044-9083-70D3ABB3121B}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2611,1047 +2526,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>15</v>
+        <v>0.9859</v>
       </c>
       <c r="E2" s="4">
-        <v>0.9859</v>
+        <v>0.9899</v>
       </c>
       <c r="F2" s="4">
         <v>0.9899</v>
       </c>
       <c r="G2" s="4">
-        <v>0.9899</v>
+        <v>0.98180000000000001</v>
       </c>
       <c r="H2" s="4">
-        <v>0.98180000000000001</v>
+        <v>0.92820000000000003</v>
       </c>
       <c r="I2" s="4">
-        <v>0.92820000000000003</v>
+        <v>0.95389999999999997</v>
       </c>
       <c r="J2" s="4">
-        <v>0.95389999999999997</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.95420000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>17</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="E3" s="4">
-        <v>0.98699999999999999</v>
+        <v>0.99139999999999995</v>
       </c>
       <c r="F3" s="4">
         <v>0.99139999999999995</v>
       </c>
       <c r="G3" s="4">
-        <v>0.99139999999999995</v>
+        <v>0.97660000000000002</v>
       </c>
       <c r="H3" s="4">
-        <v>0.97660000000000002</v>
+        <v>0.95979999999999999</v>
       </c>
       <c r="I3" s="4">
-        <v>0.95979999999999999</v>
+        <v>0.96730000000000005</v>
       </c>
       <c r="J3" s="4">
-        <v>0.96730000000000005</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.96809999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>14</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="E4" s="4">
-        <v>0.98860000000000003</v>
+        <v>0.99209999999999998</v>
       </c>
       <c r="F4" s="4">
         <v>0.99209999999999998</v>
       </c>
       <c r="G4" s="4">
-        <v>0.99209999999999998</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="H4" s="4">
         <v>0.96840000000000004</v>
       </c>
       <c r="I4" s="4">
+        <v>0.96730000000000005</v>
+      </c>
+      <c r="J4" s="4">
         <v>0.96840000000000004</v>
       </c>
-      <c r="J4" s="4">
-        <v>0.96730000000000005</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0.96840000000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>15</v>
+        <v>0.98909999999999998</v>
       </c>
       <c r="E5" s="4">
-        <v>0.98909999999999998</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="F5" s="4">
-        <v>0.99219999999999997</v>
+        <v>0.99229999999999996</v>
       </c>
       <c r="G5" s="4">
-        <v>0.99229999999999996</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="H5" s="4">
-        <v>0.95199999999999996</v>
+        <v>0.96840000000000004</v>
       </c>
       <c r="I5" s="4">
-        <v>0.96840000000000004</v>
+        <v>0.95840000000000003</v>
       </c>
       <c r="J5" s="4">
-        <v>0.95840000000000003</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.96009999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>25</v>
+        <v>0.98770000000000002</v>
       </c>
       <c r="E6" s="4">
-        <v>0.98770000000000002</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="F6" s="4">
         <v>0.99109999999999998</v>
       </c>
       <c r="G6" s="4">
-        <v>0.99109999999999998</v>
+        <v>0.97099999999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>0.97099999999999997</v>
+        <v>0.96260000000000001</v>
       </c>
       <c r="I6" s="4">
-        <v>0.96260000000000001</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="J6" s="4">
-        <v>0.96579999999999999</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.96679999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9877±0.0013</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9877±0.0013</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9913±0.0009</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.9913±0.0009</v>
+        <f t="shared" si="0"/>
+        <v>0.9914±0.0010</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9914±0.0010</v>
+        <v>0.9700±0.0113</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9700±0.0113</v>
+        <v>0.9575±0.0168</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9575±0.0168</v>
+        <v>0.9625±0.0061</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9625±0.0061</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9635±0.0062</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>25</v>
+        <v>0.93089999999999995</v>
       </c>
       <c r="E8" s="4">
-        <v>0.93089999999999995</v>
+        <v>0.9173</v>
       </c>
       <c r="F8" s="4">
-        <v>0.9173</v>
+        <v>0.91739999999999999</v>
       </c>
       <c r="G8" s="4">
-        <v>0.91739999999999999</v>
+        <v>0.82389999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>0.82389999999999997</v>
+        <v>0.80830000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>0.80830000000000002</v>
+        <v>0.84140000000000004</v>
       </c>
       <c r="J8" s="4">
-        <v>0.84140000000000004</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.81599999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>14</v>
+        <v>0.9234</v>
       </c>
       <c r="E9" s="4">
-        <v>0.9234</v>
+        <v>0.90490000000000004</v>
       </c>
       <c r="F9" s="4">
-        <v>0.90490000000000004</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="G9" s="4">
-        <v>0.90500000000000003</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="H9" s="4">
-        <v>0.82299999999999995</v>
+        <v>0.77890000000000004</v>
       </c>
       <c r="I9" s="4">
-        <v>0.77890000000000004</v>
+        <v>0.83079999999999998</v>
       </c>
       <c r="J9" s="4">
-        <v>0.83079999999999998</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.80030000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>20</v>
+        <v>0.92179999999999995</v>
       </c>
       <c r="E10" s="4">
-        <v>0.92179999999999995</v>
+        <v>0.9083</v>
       </c>
       <c r="F10" s="4">
-        <v>0.9083</v>
+        <v>0.90839999999999999</v>
       </c>
       <c r="G10" s="4">
-        <v>0.90839999999999999</v>
+        <v>0.79969999999999997</v>
       </c>
       <c r="H10" s="4">
-        <v>0.79969999999999997</v>
+        <v>0.83420000000000005</v>
       </c>
       <c r="I10" s="4">
-        <v>0.83420000000000005</v>
+        <v>0.83679999999999999</v>
       </c>
       <c r="J10" s="4">
-        <v>0.83679999999999999</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.81659999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>29</v>
+        <v>0.92669999999999997</v>
       </c>
       <c r="E11" s="4">
-        <v>0.92669999999999997</v>
+        <v>0.91449999999999998</v>
       </c>
       <c r="F11" s="4">
-        <v>0.91449999999999998</v>
+        <v>0.91459999999999997</v>
       </c>
       <c r="G11" s="4">
-        <v>0.91459999999999997</v>
+        <v>0.85389999999999999</v>
       </c>
       <c r="H11" s="4">
-        <v>0.85389999999999999</v>
+        <v>0.7772</v>
       </c>
       <c r="I11" s="4">
-        <v>0.7772</v>
+        <v>0.84509999999999996</v>
       </c>
       <c r="J11" s="4">
-        <v>0.84509999999999996</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.81369999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>17</v>
+        <v>0.91869999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.91869999999999996</v>
+        <v>0.90529999999999999</v>
       </c>
       <c r="F12" s="4">
-        <v>0.90529999999999999</v>
+        <v>0.90539999999999998</v>
       </c>
       <c r="G12" s="4">
-        <v>0.90539999999999998</v>
+        <v>0.8165</v>
       </c>
       <c r="H12" s="4">
-        <v>0.8165</v>
+        <v>0.76859999999999995</v>
       </c>
       <c r="I12" s="4">
-        <v>0.76859999999999995</v>
+        <v>0.82410000000000005</v>
       </c>
       <c r="J12" s="4">
-        <v>0.82410000000000005</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.79179999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9243±0.0047</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9243±0.0047</v>
+        <f t="shared" si="1"/>
+        <v>0.9101±0.0056</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9101±0.0056</v>
+        <v>0.9102±0.0056</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9102±0.0056</v>
+        <v>0.8234±0.0196</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8234±0.0196</v>
+        <v>0.7934±0.0273</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7934±0.0273</v>
+        <v>0.8356±0.0084</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8356±0.0084</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8077±0.0111</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
+        <v>0.9708</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.95640000000000003</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.95650000000000002</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.92420000000000002</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.91669999999999996</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.89890000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="4">
-        <v>0.9708</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0.95640000000000003</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.95650000000000002</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0.92420000000000002</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0.91669999999999996</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0.89890000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
+        <v>0.97519999999999996</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.96619999999999995</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.96630000000000005</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.94640000000000002</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.87880000000000003</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.93149999999999999</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.9113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0.97519999999999996</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0.96619999999999995</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.96630000000000005</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0.94640000000000002</v>
-      </c>
-      <c r="I15" s="4">
-        <v>0.87880000000000003</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.93149999999999999</v>
-      </c>
-      <c r="K15" s="4">
-        <v>0.9113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>11</v>
+        <v>0.96860000000000002</v>
       </c>
       <c r="E16" s="4">
-        <v>0.96860000000000002</v>
+        <v>0.9496</v>
       </c>
       <c r="F16" s="4">
-        <v>0.9496</v>
+        <v>0.94969999999999999</v>
       </c>
       <c r="G16" s="4">
-        <v>0.94969999999999999</v>
+        <v>0.90849999999999997</v>
       </c>
       <c r="H16" s="4">
-        <v>0.90849999999999997</v>
+        <v>0.90259999999999996</v>
       </c>
       <c r="I16" s="4">
-        <v>0.90259999999999996</v>
+        <v>0.92449999999999999</v>
       </c>
       <c r="J16" s="4">
-        <v>0.92449999999999999</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.90549999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>24</v>
+        <v>0.97240000000000004</v>
       </c>
       <c r="E17" s="4">
-        <v>0.97240000000000004</v>
+        <v>0.95889999999999997</v>
       </c>
       <c r="F17" s="4">
         <v>0.95889999999999997</v>
       </c>
       <c r="G17" s="4">
-        <v>0.95889999999999997</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="H17" s="4">
-        <v>0.93100000000000005</v>
+        <v>0.90480000000000005</v>
       </c>
       <c r="I17" s="4">
-        <v>0.90480000000000005</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="J17" s="4">
-        <v>0.93500000000000005</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.91769999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>30</v>
+        <v>0.97460000000000002</v>
       </c>
       <c r="E18" s="4">
-        <v>0.97460000000000002</v>
+        <v>0.96550000000000002</v>
       </c>
       <c r="F18" s="4">
         <v>0.96550000000000002</v>
       </c>
       <c r="G18" s="4">
-        <v>0.96550000000000002</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>0.92310000000000003</v>
+        <v>0.90910000000000002</v>
       </c>
       <c r="I18" s="4">
-        <v>0.90910000000000002</v>
+        <v>0.93320000000000003</v>
       </c>
       <c r="J18" s="4">
-        <v>0.93320000000000003</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.91600000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9723±0.0027</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9723±0.0027</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9593±0.0069</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.9593±0.0069</v>
+        <f t="shared" si="2"/>
+        <v>0.9594±0.0068</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9594±0.0068</v>
+        <v>0.9168±0.0271</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9168±0.0271</v>
+        <v>0.9039±0.0164</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9039±0.0164</v>
+        <v>0.9282±0.0076</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9282±0.0076</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.9099±0.0078</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>28</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="E20" s="4">
-        <v>0.98499999999999999</v>
+        <v>0.96579999999999999</v>
       </c>
       <c r="F20" s="4">
-        <v>0.96579999999999999</v>
+        <v>0.96609999999999996</v>
       </c>
       <c r="G20" s="4">
-        <v>0.96609999999999996</v>
+        <v>0.94440000000000002</v>
       </c>
       <c r="H20" s="4">
-        <v>0.94440000000000002</v>
+        <v>0.91069999999999995</v>
       </c>
       <c r="I20" s="4">
-        <v>0.91069999999999995</v>
+        <v>0.96330000000000005</v>
       </c>
       <c r="J20" s="4">
-        <v>0.96330000000000005</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.92730000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>24</v>
+        <v>0.97219999999999995</v>
       </c>
       <c r="E21" s="4">
-        <v>0.97219999999999995</v>
+        <v>0.93759999999999999</v>
       </c>
       <c r="F21" s="4">
-        <v>0.93759999999999999</v>
+        <v>0.93820000000000003</v>
       </c>
       <c r="G21" s="4">
-        <v>0.93820000000000003</v>
+        <v>0.92310000000000003</v>
       </c>
       <c r="H21" s="4">
-        <v>0.92310000000000003</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="I21" s="4">
-        <v>0.85709999999999997</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="J21" s="4">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>25</v>
+        <v>0.97970000000000002</v>
       </c>
       <c r="E22" s="4">
-        <v>0.97970000000000002</v>
+        <v>0.9355</v>
       </c>
       <c r="F22" s="4">
-        <v>0.9355</v>
+        <v>0.93730000000000002</v>
       </c>
       <c r="G22" s="4">
-        <v>0.93730000000000002</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="H22" s="4">
-        <v>0.89659999999999995</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="I22" s="4">
-        <v>0.92859999999999998</v>
+        <v>0.95409999999999995</v>
       </c>
       <c r="J22" s="4">
-        <v>0.95409999999999995</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.9123</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>30</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="E23" s="4">
-        <v>0.98560000000000003</v>
+        <v>0.97260000000000002</v>
       </c>
       <c r="F23" s="4">
-        <v>0.97260000000000002</v>
+        <v>0.9728</v>
       </c>
       <c r="G23" s="4">
-        <v>0.9728</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="H23" s="4">
         <v>0.92859999999999998</v>
       </c>
       <c r="I23" s="4">
+        <v>0.96330000000000005</v>
+      </c>
+      <c r="J23" s="4">
         <v>0.92859999999999998</v>
       </c>
-      <c r="J23" s="4">
-        <v>0.96330000000000005</v>
-      </c>
-      <c r="K23" s="4">
-        <v>0.92859999999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>24</v>
+        <v>0.97719999999999996</v>
       </c>
       <c r="E24" s="4">
-        <v>0.97719999999999996</v>
+        <v>0.94450000000000001</v>
       </c>
       <c r="F24" s="4">
-        <v>0.94450000000000001</v>
+        <v>0.94510000000000005</v>
       </c>
       <c r="G24" s="4">
-        <v>0.94510000000000005</v>
+        <v>0.89290000000000003</v>
       </c>
       <c r="H24" s="4">
         <v>0.89290000000000003</v>
       </c>
       <c r="I24" s="4">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="J24" s="4">
         <v>0.89290000000000003</v>
       </c>
-      <c r="J24" s="4">
-        <v>0.94499999999999995</v>
-      </c>
-      <c r="K24" s="4">
-        <v>0.89290000000000003</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9799±0.0056</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9799±0.0056</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9512±0.0169</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9512±0.0169</v>
+        <f t="shared" si="3"/>
+        <v>0.9519±0.0165</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9519±0.0165</v>
+        <v>0.9171±0.0219</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9171±0.0219</v>
+        <v>0.9036±0.0299</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9036±0.0299</v>
+        <v>0.9541±0.0092</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9541±0.0092</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9100±0.0186</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>28</v>
+        <v>0.98650000000000004</v>
       </c>
       <c r="E26" s="4">
-        <v>0.98650000000000004</v>
+        <v>0.99060000000000004</v>
       </c>
       <c r="F26" s="4">
         <v>0.99060000000000004</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99060000000000004</v>
+        <v>0.94950000000000001</v>
       </c>
       <c r="H26" s="4">
+        <v>0.96909999999999996</v>
+      </c>
+      <c r="I26" s="4">
         <v>0.94950000000000001</v>
       </c>
-      <c r="I26" s="4">
-        <v>0.96909999999999996</v>
-      </c>
       <c r="J26" s="4">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.95920000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>27</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="E27" s="4">
-        <v>0.98699999999999999</v>
+        <v>0.99170000000000003</v>
       </c>
       <c r="F27" s="4">
         <v>0.99170000000000003</v>
       </c>
       <c r="G27" s="4">
-        <v>0.99170000000000003</v>
+        <v>0.94920000000000004</v>
       </c>
       <c r="H27" s="4">
-        <v>0.94920000000000004</v>
+        <v>0.96389999999999998</v>
       </c>
       <c r="I27" s="4">
-        <v>0.96389999999999998</v>
+        <v>0.94640000000000002</v>
       </c>
       <c r="J27" s="4">
-        <v>0.94640000000000002</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.95650000000000002</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>30</v>
+        <v>0.98019999999999996</v>
       </c>
       <c r="E28" s="4">
-        <v>0.98019999999999996</v>
+        <v>0.9869</v>
       </c>
       <c r="F28" s="4">
         <v>0.9869</v>
       </c>
       <c r="G28" s="4">
-        <v>0.9869</v>
+        <v>0.94869999999999999</v>
       </c>
       <c r="H28" s="4">
-        <v>0.94869999999999999</v>
+        <v>0.9536</v>
       </c>
       <c r="I28" s="4">
-        <v>0.9536</v>
+        <v>0.94010000000000005</v>
       </c>
       <c r="J28" s="4">
-        <v>0.94010000000000005</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.95120000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>26</v>
+        <v>0.98429999999999995</v>
       </c>
       <c r="E29" s="4">
-        <v>0.98429999999999995</v>
+        <v>0.98880000000000001</v>
       </c>
       <c r="F29" s="4">
         <v>0.98880000000000001</v>
       </c>
       <c r="G29" s="4">
-        <v>0.98880000000000001</v>
+        <v>0.95479999999999998</v>
       </c>
       <c r="H29" s="4">
-        <v>0.95479999999999998</v>
+        <v>0.97940000000000005</v>
       </c>
       <c r="I29" s="4">
-        <v>0.97940000000000005</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="J29" s="4">
-        <v>0.95899999999999996</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.96689999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>30</v>
+        <v>0.98170000000000002</v>
       </c>
       <c r="E30" s="4">
-        <v>0.98170000000000002</v>
+        <v>0.98780000000000001</v>
       </c>
       <c r="F30" s="4">
         <v>0.98780000000000001</v>
       </c>
       <c r="G30" s="4">
-        <v>0.98780000000000001</v>
+        <v>0.94330000000000003</v>
       </c>
       <c r="H30" s="4">
         <v>0.94330000000000003</v>
       </c>
       <c r="I30" s="4">
+        <v>0.93059999999999998</v>
+      </c>
+      <c r="J30" s="4">
         <v>0.94330000000000003</v>
       </c>
-      <c r="J30" s="4">
-        <v>0.93059999999999998</v>
-      </c>
-      <c r="K30" s="4">
-        <v>0.94330000000000003</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9839±0.0030</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9839±0.0030</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9892±0.0020</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9892±0.0020</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9892±0.0020</v>
+        <v>0.9491±0.0041</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9491±0.0041</v>
+        <v>0.9619±0.0139</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9619±0.0139</v>
+        <v>0.9451±0.0106</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9451±0.0106</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9554±0.0088</v>
       </c>
@@ -3699,186 +3532,168 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>11</v>
+        <v>0.88919999999999999</v>
       </c>
       <c r="E2" s="4">
-        <v>0.88919999999999999</v>
+        <v>0.87390000000000001</v>
       </c>
       <c r="F2" s="4">
-        <v>0.87390000000000001</v>
+        <v>0.87419999999999998</v>
       </c>
       <c r="G2" s="4">
-        <v>0.87419999999999998</v>
+        <v>0.75509999999999999</v>
       </c>
       <c r="H2" s="4">
-        <v>0.75509999999999999</v>
+        <v>0.88419999999999999</v>
       </c>
       <c r="I2" s="4">
-        <v>0.88419999999999999</v>
+        <v>0.80869999999999997</v>
       </c>
       <c r="J2" s="4">
-        <v>0.80869999999999997</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.8145</v>
       </c>
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>22</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="E3" s="4">
-        <v>0.89400000000000002</v>
+        <v>0.87639999999999996</v>
       </c>
       <c r="F3" s="4">
-        <v>0.87639999999999996</v>
+        <v>0.87670000000000003</v>
       </c>
       <c r="G3" s="4">
-        <v>0.87670000000000003</v>
+        <v>0.79379999999999995</v>
       </c>
       <c r="H3" s="4">
-        <v>0.79379999999999995</v>
+        <v>0.8105</v>
       </c>
       <c r="I3" s="4">
-        <v>0.8105</v>
+        <v>0.81</v>
       </c>
       <c r="J3" s="4">
-        <v>0.81</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.80210000000000004</v>
       </c>
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>25</v>
+        <v>0.89190000000000003</v>
       </c>
       <c r="E4" s="4">
-        <v>0.89190000000000003</v>
+        <v>0.88290000000000002</v>
       </c>
       <c r="F4" s="4">
-        <v>0.88290000000000002</v>
+        <v>0.8831</v>
       </c>
       <c r="G4" s="4">
-        <v>0.8831</v>
+        <v>0.83089999999999997</v>
       </c>
       <c r="H4" s="4">
-        <v>0.83089999999999997</v>
+        <v>0.73680000000000001</v>
       </c>
       <c r="I4" s="4">
-        <v>0.73680000000000001</v>
+        <v>0.80369999999999997</v>
       </c>
       <c r="J4" s="4">
-        <v>0.80369999999999997</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.78100000000000003</v>
       </c>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>18</v>
+        <v>0.89670000000000005</v>
       </c>
       <c r="E5" s="4">
-        <v>0.89670000000000005</v>
+        <v>0.88180000000000003</v>
       </c>
       <c r="F5" s="4">
-        <v>0.88180000000000003</v>
+        <v>0.8821</v>
       </c>
       <c r="G5" s="4">
-        <v>0.8821</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="H5" s="4">
-        <v>0.77800000000000002</v>
+        <v>0.8579</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8579</v>
+        <v>0.81630000000000003</v>
       </c>
       <c r="J5" s="4">
-        <v>0.81630000000000003</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.81599999999999995</v>
       </c>
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>11</v>
+        <v>0.8962</v>
       </c>
       <c r="E6" s="4">
-        <v>0.8962</v>
+        <v>0.87629999999999997</v>
       </c>
       <c r="F6" s="4">
-        <v>0.87629999999999997</v>
+        <v>0.87660000000000005</v>
       </c>
       <c r="G6" s="4">
-        <v>0.87660000000000005</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="H6" s="4">
-        <v>0.80100000000000005</v>
+        <v>0.82630000000000003</v>
       </c>
       <c r="I6" s="4">
-        <v>0.82630000000000003</v>
+        <v>0.82</v>
       </c>
       <c r="J6" s="4">
-        <v>0.82</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.8135</v>
       </c>
       <c r="L6" s="4"/>
@@ -3887,212 +3702,196 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.8936±0.0031</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.8936±0.0031</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.8783±0.0039</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.8783±0.0039</v>
+        <f t="shared" si="0"/>
+        <v>0.8785±0.0039</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8785±0.0039</v>
+        <v>0.7918±0.0281</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.7918±0.0281</v>
+        <v>0.8231±0.0560</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8231±0.0560</v>
+        <v>0.8117±0.0064</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8117±0.0064</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8054±0.0147</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>21</v>
+        <v>0.87160000000000004</v>
       </c>
       <c r="E8" s="4">
-        <v>0.87160000000000004</v>
+        <v>0.88029999999999997</v>
       </c>
       <c r="F8" s="4">
-        <v>0.88029999999999997</v>
+        <v>0.88039999999999996</v>
       </c>
       <c r="G8" s="4">
-        <v>0.88039999999999996</v>
+        <v>0.74970000000000003</v>
       </c>
       <c r="H8" s="4">
-        <v>0.74970000000000003</v>
+        <v>0.83909999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>0.83909999999999996</v>
+        <v>0.78120000000000001</v>
       </c>
       <c r="J8" s="4">
-        <v>0.78120000000000001</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.79190000000000005</v>
       </c>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>22</v>
+        <v>0.87270000000000003</v>
       </c>
       <c r="E9" s="4">
-        <v>0.87270000000000003</v>
+        <v>0.87719999999999998</v>
       </c>
       <c r="F9" s="4">
-        <v>0.87719999999999998</v>
+        <v>0.87729999999999997</v>
       </c>
       <c r="G9" s="4">
-        <v>0.87729999999999997</v>
+        <v>0.76390000000000002</v>
       </c>
       <c r="H9" s="4">
-        <v>0.76390000000000002</v>
+        <v>0.82120000000000004</v>
       </c>
       <c r="I9" s="4">
-        <v>0.82120000000000004</v>
+        <v>0.7853</v>
       </c>
       <c r="J9" s="4">
-        <v>0.7853</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.79149999999999998</v>
       </c>
       <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>18</v>
+        <v>0.88060000000000005</v>
       </c>
       <c r="E10" s="4">
-        <v>0.88060000000000005</v>
+        <v>0.8871</v>
       </c>
       <c r="F10" s="4">
-        <v>0.8871</v>
+        <v>0.88719999999999999</v>
       </c>
       <c r="G10" s="4">
-        <v>0.88719999999999999</v>
+        <v>0.80359999999999998</v>
       </c>
       <c r="H10" s="4">
-        <v>0.80359999999999998</v>
+        <v>0.80930000000000002</v>
       </c>
       <c r="I10" s="4">
-        <v>0.80930000000000002</v>
+        <v>0.80720000000000003</v>
       </c>
       <c r="J10" s="4">
-        <v>0.80720000000000003</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.80640000000000001</v>
       </c>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>21</v>
+        <v>0.87760000000000005</v>
       </c>
       <c r="E11" s="4">
-        <v>0.87760000000000005</v>
+        <v>0.88180000000000003</v>
       </c>
       <c r="F11" s="4">
-        <v>0.88180000000000003</v>
+        <v>0.88190000000000002</v>
       </c>
       <c r="G11" s="4">
-        <v>0.88190000000000002</v>
+        <v>0.72430000000000005</v>
       </c>
       <c r="H11" s="4">
-        <v>0.72430000000000005</v>
+        <v>0.87370000000000003</v>
       </c>
       <c r="I11" s="4">
-        <v>0.87370000000000003</v>
+        <v>0.77229999999999999</v>
       </c>
       <c r="J11" s="4">
-        <v>0.77229999999999999</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.79200000000000004</v>
       </c>
       <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>20</v>
+        <v>0.87129999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.87129999999999996</v>
+        <v>0.87019999999999997</v>
       </c>
       <c r="F12" s="4">
-        <v>0.87019999999999997</v>
+        <v>0.87029999999999996</v>
       </c>
       <c r="G12" s="4">
-        <v>0.87029999999999996</v>
+        <v>0.79569999999999996</v>
       </c>
       <c r="H12" s="4">
-        <v>0.79569999999999996</v>
+        <v>0.79859999999999998</v>
       </c>
       <c r="I12" s="4">
-        <v>0.79859999999999998</v>
+        <v>0.79830000000000001</v>
       </c>
       <c r="J12" s="4">
-        <v>0.79830000000000001</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.79710000000000003</v>
       </c>
       <c r="L12" s="4"/>
@@ -4101,212 +3900,196 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8748±0.0041</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8748±0.0041</v>
+        <f t="shared" si="1"/>
+        <v>0.8793±0.0062</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8793±0.0062</v>
+        <v>0.8794±0.0062</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8794±0.0062</v>
+        <v>0.7674±0.0328</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7674±0.0328</v>
+        <v>0.8284±0.0295</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8284±0.0295</v>
+        <v>0.7889±0.0139</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7889±0.0139</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7958±0.0064</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>29</v>
+        <v>0.73209999999999997</v>
       </c>
       <c r="E14" s="4">
-        <v>0.73209999999999997</v>
+        <v>0.75739999999999996</v>
       </c>
       <c r="F14" s="4">
-        <v>0.75739999999999996</v>
+        <v>0.75770000000000004</v>
       </c>
       <c r="G14" s="4">
-        <v>0.75770000000000004</v>
+        <v>0.72450000000000003</v>
       </c>
       <c r="H14" s="4">
-        <v>0.72450000000000003</v>
+        <v>0.73740000000000006</v>
       </c>
       <c r="I14" s="4">
-        <v>0.73740000000000006</v>
+        <v>0.68520000000000003</v>
       </c>
       <c r="J14" s="4">
-        <v>0.68520000000000003</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.73089999999999999</v>
       </c>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>0.75580000000000003</v>
       </c>
       <c r="E15" s="4">
-        <v>0.75580000000000003</v>
+        <v>0.77739999999999998</v>
       </c>
       <c r="F15" s="4">
-        <v>0.77739999999999998</v>
+        <v>0.77769999999999995</v>
       </c>
       <c r="G15" s="4">
-        <v>0.77769999999999995</v>
+        <v>0.747</v>
       </c>
       <c r="H15" s="4">
-        <v>0.747</v>
+        <v>0.74329999999999996</v>
       </c>
       <c r="I15" s="4">
-        <v>0.74329999999999996</v>
+        <v>0.70520000000000005</v>
       </c>
       <c r="J15" s="4">
-        <v>0.70520000000000005</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.74519999999999997</v>
       </c>
       <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>20</v>
+        <v>0.75660000000000005</v>
       </c>
       <c r="E16" s="4">
-        <v>0.75660000000000005</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="F16" s="4">
-        <v>0.77600000000000002</v>
+        <v>0.77629999999999999</v>
       </c>
       <c r="G16" s="4">
-        <v>0.77629999999999999</v>
+        <v>0.70909999999999995</v>
       </c>
       <c r="H16" s="4">
-        <v>0.70909999999999995</v>
+        <v>0.85189999999999999</v>
       </c>
       <c r="I16" s="4">
-        <v>0.85189999999999999</v>
+        <v>0.71150000000000002</v>
       </c>
       <c r="J16" s="4">
-        <v>0.71150000000000002</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.77400000000000002</v>
       </c>
       <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>13</v>
+        <v>0.73029999999999995</v>
       </c>
       <c r="E17" s="4">
-        <v>0.73029999999999995</v>
+        <v>0.75660000000000005</v>
       </c>
       <c r="F17" s="4">
-        <v>0.75660000000000005</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="G17" s="4">
-        <v>0.75700000000000001</v>
+        <v>0.70569999999999999</v>
       </c>
       <c r="H17" s="4">
-        <v>0.70569999999999999</v>
+        <v>0.79759999999999998</v>
       </c>
       <c r="I17" s="4">
-        <v>0.79759999999999998</v>
+        <v>0.68979999999999997</v>
       </c>
       <c r="J17" s="4">
-        <v>0.68979999999999997</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.74880000000000002</v>
       </c>
       <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>11</v>
+        <v>0.76919999999999999</v>
       </c>
       <c r="E18" s="4">
-        <v>0.76919999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="F18" s="4">
-        <v>0.78</v>
+        <v>0.78090000000000004</v>
       </c>
       <c r="G18" s="4">
-        <v>0.78090000000000004</v>
+        <v>0.67959999999999998</v>
       </c>
       <c r="H18" s="4">
-        <v>0.67959999999999998</v>
+        <v>0.91910000000000003</v>
       </c>
       <c r="I18" s="4">
-        <v>0.91910000000000003</v>
+        <v>0.70179999999999998</v>
       </c>
       <c r="J18" s="4">
-        <v>0.70179999999999998</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.78139999999999998</v>
       </c>
       <c r="L18" s="4"/>
@@ -4315,212 +4098,196 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7488±0.0169</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7488±0.0169</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7695±0.0115</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7695±0.0115</v>
+        <f t="shared" si="2"/>
+        <v>0.7699±0.0116</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7699±0.0116</v>
+        <v>0.7132±0.0249</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7132±0.0249</v>
+        <v>0.8099±0.0767</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8099±0.0767</v>
+        <v>0.6987±0.0109</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6987±0.0109</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.7561±0.0210</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>26</v>
+        <v>0.88180000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>0.88180000000000003</v>
+        <v>0.87260000000000004</v>
       </c>
       <c r="F20" s="4">
-        <v>0.87260000000000004</v>
+        <v>0.87309999999999999</v>
       </c>
       <c r="G20" s="4">
-        <v>0.87309999999999999</v>
+        <v>0.78339999999999999</v>
       </c>
       <c r="H20" s="4">
-        <v>0.78339999999999999</v>
+        <v>0.83109999999999995</v>
       </c>
       <c r="I20" s="4">
-        <v>0.83109999999999995</v>
+        <v>0.82850000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>0.82850000000000001</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.80659999999999998</v>
       </c>
       <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>19</v>
+        <v>0.86209999999999998</v>
       </c>
       <c r="E21" s="4">
-        <v>0.86209999999999998</v>
+        <v>0.85309999999999997</v>
       </c>
       <c r="F21" s="4">
-        <v>0.85309999999999997</v>
+        <v>0.85370000000000001</v>
       </c>
       <c r="G21" s="4">
-        <v>0.85370000000000001</v>
+        <v>0.73580000000000001</v>
       </c>
       <c r="H21" s="4">
-        <v>0.73580000000000001</v>
+        <v>0.79049999999999998</v>
       </c>
       <c r="I21" s="4">
-        <v>0.79049999999999998</v>
+        <v>0.78779999999999994</v>
       </c>
       <c r="J21" s="4">
-        <v>0.78779999999999994</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.76219999999999999</v>
       </c>
       <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>18</v>
+        <v>0.86960000000000004</v>
       </c>
       <c r="E22" s="4">
-        <v>0.86960000000000004</v>
+        <v>0.85589999999999999</v>
       </c>
       <c r="F22" s="4">
-        <v>0.85589999999999999</v>
+        <v>0.85660000000000003</v>
       </c>
       <c r="G22" s="4">
-        <v>0.85660000000000003</v>
+        <v>0.79020000000000001</v>
       </c>
       <c r="H22" s="4">
-        <v>0.79020000000000001</v>
+        <v>0.76349999999999996</v>
       </c>
       <c r="I22" s="4">
-        <v>0.76349999999999996</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="J22" s="4">
-        <v>0.81100000000000005</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.77659999999999996</v>
       </c>
       <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>30</v>
+        <v>0.87570000000000003</v>
       </c>
       <c r="E23" s="4">
-        <v>0.87570000000000003</v>
+        <v>0.85750000000000004</v>
       </c>
       <c r="F23" s="4">
-        <v>0.85750000000000004</v>
+        <v>0.85809999999999997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.85809999999999997</v>
+        <v>0.78669999999999995</v>
       </c>
       <c r="H23" s="4">
-        <v>0.78669999999999995</v>
+        <v>0.79730000000000001</v>
       </c>
       <c r="I23" s="4">
-        <v>0.79730000000000001</v>
+        <v>0.81979999999999997</v>
       </c>
       <c r="J23" s="4">
-        <v>0.81979999999999997</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.79190000000000005</v>
       </c>
       <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>26</v>
+        <v>0.87980000000000003</v>
       </c>
       <c r="E24" s="4">
-        <v>0.87980000000000003</v>
+        <v>0.85350000000000004</v>
       </c>
       <c r="F24" s="4">
-        <v>0.85350000000000004</v>
+        <v>0.85429999999999995</v>
       </c>
       <c r="G24" s="4">
-        <v>0.85429999999999995</v>
+        <v>0.75460000000000005</v>
       </c>
       <c r="H24" s="4">
-        <v>0.75460000000000005</v>
+        <v>0.83109999999999995</v>
       </c>
       <c r="I24" s="4">
-        <v>0.83109999999999995</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="J24" s="4">
-        <v>0.81100000000000005</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.79100000000000004</v>
       </c>
       <c r="L24" s="4"/>
@@ -4529,242 +4296,226 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.8738±0.0080</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.8738±0.0080</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.8585±0.0081</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.8585±0.0081</v>
+        <f t="shared" si="3"/>
+        <v>0.8592±0.0080</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8592±0.0080</v>
+        <v>0.7701±0.0238</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7701±0.0238</v>
+        <v>0.8027±0.0288</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8027±0.0288</v>
+        <v>0.8116±0.0152</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8116±0.0152</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.7857±0.0169</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>17</v>
+        <v>0.75949999999999995</v>
       </c>
       <c r="E26" s="4">
-        <v>0.75949999999999995</v>
+        <v>0.74639999999999995</v>
       </c>
       <c r="F26" s="4">
-        <v>0.74639999999999995</v>
+        <v>0.74850000000000005</v>
       </c>
       <c r="G26" s="4">
-        <v>0.74850000000000005</v>
+        <v>0.71899999999999997</v>
       </c>
       <c r="H26" s="4">
-        <v>0.71899999999999997</v>
+        <v>0.71309999999999996</v>
       </c>
       <c r="I26" s="4">
-        <v>0.71309999999999996</v>
+        <v>0.7026</v>
       </c>
       <c r="J26" s="4">
-        <v>0.7026</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.71599999999999997</v>
       </c>
       <c r="L26" s="4"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>10</v>
+        <v>0.75190000000000001</v>
       </c>
       <c r="E27" s="4">
-        <v>0.75190000000000001</v>
+        <v>0.75109999999999999</v>
       </c>
       <c r="F27" s="4">
-        <v>0.75109999999999999</v>
+        <v>0.75339999999999996</v>
       </c>
       <c r="G27" s="4">
-        <v>0.75339999999999996</v>
+        <v>0.6452</v>
       </c>
       <c r="H27" s="4">
-        <v>0.6452</v>
+        <v>0.81969999999999998</v>
       </c>
       <c r="I27" s="4">
-        <v>0.81969999999999998</v>
+        <v>0.66810000000000003</v>
       </c>
       <c r="J27" s="4">
-        <v>0.66810000000000003</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.72199999999999998</v>
       </c>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>30</v>
+        <v>0.69120000000000004</v>
       </c>
       <c r="E28" s="4">
-        <v>0.69120000000000004</v>
+        <v>0.66349999999999998</v>
       </c>
       <c r="F28" s="4">
-        <v>0.66349999999999998</v>
+        <v>0.66990000000000005</v>
       </c>
       <c r="G28" s="4">
-        <v>0.66990000000000005</v>
+        <v>0.65080000000000005</v>
       </c>
       <c r="H28" s="4">
-        <v>0.65080000000000005</v>
+        <v>0.67210000000000003</v>
       </c>
       <c r="I28" s="4">
-        <v>0.67210000000000003</v>
+        <v>0.63790000000000002</v>
       </c>
       <c r="J28" s="4">
-        <v>0.63790000000000002</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.6613</v>
       </c>
       <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>11</v>
+        <v>0.76</v>
       </c>
       <c r="E29" s="4">
-        <v>0.76</v>
+        <v>0.75339999999999996</v>
       </c>
       <c r="F29" s="4">
-        <v>0.75339999999999996</v>
+        <v>0.75570000000000004</v>
       </c>
       <c r="G29" s="4">
-        <v>0.75570000000000004</v>
+        <v>0.66669999999999996</v>
       </c>
       <c r="H29" s="4">
-        <v>0.66669999999999996</v>
+        <v>0.80330000000000001</v>
       </c>
       <c r="I29" s="4">
-        <v>0.80330000000000001</v>
+        <v>0.68530000000000002</v>
       </c>
       <c r="J29" s="4">
-        <v>0.68530000000000002</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.72860000000000003</v>
       </c>
       <c r="L29" s="4"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>15</v>
+        <v>0.74409999999999998</v>
       </c>
       <c r="E30" s="4">
-        <v>0.74409999999999998</v>
+        <v>0.73939999999999995</v>
       </c>
       <c r="F30" s="4">
-        <v>0.73939999999999995</v>
+        <v>0.74270000000000003</v>
       </c>
       <c r="G30" s="4">
-        <v>0.74270000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="H30" s="4">
-        <v>0.66</v>
+        <v>0.8115</v>
       </c>
       <c r="I30" s="4">
-        <v>0.8115</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="J30" s="4">
-        <v>0.68100000000000005</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.72789999999999999</v>
       </c>
       <c r="L30" s="4"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.7413±0.0288</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.7413±0.0288</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.7308±0.0380</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.7308±0.0380</v>
+        <f t="shared" si="4"/>
+        <v>0.7340±0.0362</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7340±0.0362</v>
+        <v>0.6683±0.0295</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.6683±0.0295</v>
+        <v>0.7639±0.0670</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7639±0.0670</v>
+        <v>0.6750±0.0241</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.6750±0.0241</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.7112±0.0283</v>
       </c>
@@ -4778,10 +4529,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45275180-57AC-4BB6-B1CC-6E162588BEA5}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4812,1047 +4563,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>26</v>
+        <v>0.95469999999999999</v>
       </c>
       <c r="E2" s="4">
-        <v>0.95469999999999999</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="F2" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.94640000000000002</v>
       </c>
       <c r="G2" s="4">
-        <v>0.94640000000000002</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="H2" s="4">
-        <v>0.90400000000000003</v>
+        <v>0.8861</v>
       </c>
       <c r="I2" s="4">
-        <v>0.8861</v>
+        <v>0.90129999999999999</v>
       </c>
       <c r="J2" s="4">
-        <v>0.90129999999999999</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.89500000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>13</v>
+        <v>0.95689999999999997</v>
       </c>
       <c r="E3" s="4">
-        <v>0.95689999999999997</v>
+        <v>0.95069999999999999</v>
       </c>
       <c r="F3" s="4">
-        <v>0.95069999999999999</v>
+        <v>0.95079999999999998</v>
       </c>
       <c r="G3" s="4">
-        <v>0.95079999999999998</v>
+        <v>0.87319999999999998</v>
       </c>
       <c r="H3" s="4">
-        <v>0.87319999999999998</v>
+        <v>0.90349999999999997</v>
       </c>
       <c r="I3" s="4">
-        <v>0.90349999999999997</v>
+        <v>0.89190000000000003</v>
       </c>
       <c r="J3" s="4">
-        <v>0.89190000000000003</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.8881</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>19</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="E4" s="4">
-        <v>0.95599999999999996</v>
+        <v>0.94510000000000005</v>
       </c>
       <c r="F4" s="4">
-        <v>0.94510000000000005</v>
+        <v>0.94520000000000004</v>
       </c>
       <c r="G4" s="4">
-        <v>0.94520000000000004</v>
+        <v>0.84789999999999999</v>
       </c>
       <c r="H4" s="4">
-        <v>0.84789999999999999</v>
+        <v>0.93810000000000004</v>
       </c>
       <c r="I4" s="4">
-        <v>0.93810000000000004</v>
+        <v>0.89070000000000005</v>
       </c>
       <c r="J4" s="4">
         <v>0.89070000000000005</v>
       </c>
-      <c r="K4" s="4">
-        <v>0.89070000000000005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>15</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="E5" s="4">
-        <v>0.95699999999999996</v>
+        <v>0.95150000000000001</v>
       </c>
       <c r="F5" s="4">
-        <v>0.95150000000000001</v>
+        <v>0.9516</v>
       </c>
       <c r="G5" s="4">
-        <v>0.9516</v>
+        <v>0.87350000000000005</v>
       </c>
       <c r="H5" s="4">
-        <v>0.87350000000000005</v>
+        <v>0.92330000000000001</v>
       </c>
       <c r="I5" s="4">
-        <v>0.92330000000000001</v>
+        <v>0.90010000000000001</v>
       </c>
       <c r="J5" s="4">
-        <v>0.90010000000000001</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.89770000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>27</v>
+        <v>0.95740000000000003</v>
       </c>
       <c r="E6" s="4">
-        <v>0.95740000000000003</v>
+        <v>0.95140000000000002</v>
       </c>
       <c r="F6" s="4">
         <v>0.95140000000000002</v>
       </c>
       <c r="G6" s="4">
-        <v>0.95140000000000002</v>
+        <v>0.89359999999999995</v>
       </c>
       <c r="H6" s="4">
         <v>0.89359999999999995</v>
       </c>
       <c r="I6" s="4">
+        <v>0.89890000000000003</v>
+      </c>
+      <c r="J6" s="4">
         <v>0.89359999999999995</v>
       </c>
-      <c r="J6" s="4">
-        <v>0.89890000000000003</v>
-      </c>
-      <c r="K6" s="4">
-        <v>0.89359999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9564±0.0011</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9564±0.0011</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9490±0.0031</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.9490±0.0031</v>
+        <f t="shared" si="0"/>
+        <v>0.9491±0.0030</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9491±0.0030</v>
+        <v>0.8784±0.0216</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8784±0.0216</v>
+        <v>0.9089±0.0215</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9089±0.0215</v>
+        <v>0.8966±0.0049</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8966±0.0049</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8930±0.0037</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>29</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="E8" s="4">
-        <v>0.95299999999999996</v>
+        <v>0.95289999999999997</v>
       </c>
       <c r="F8" s="4">
         <v>0.95289999999999997</v>
       </c>
       <c r="G8" s="4">
-        <v>0.95289999999999997</v>
+        <v>0.8579</v>
       </c>
       <c r="H8" s="4">
-        <v>0.8579</v>
+        <v>0.90710000000000002</v>
       </c>
       <c r="I8" s="4">
-        <v>0.90710000000000002</v>
+        <v>0.87980000000000003</v>
       </c>
       <c r="J8" s="4">
-        <v>0.87980000000000003</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.88180000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>27</v>
+        <v>0.94479999999999997</v>
       </c>
       <c r="E9" s="4">
-        <v>0.94479999999999997</v>
+        <v>0.94320000000000004</v>
       </c>
       <c r="F9" s="4">
-        <v>0.94320000000000004</v>
+        <v>0.94330000000000003</v>
       </c>
       <c r="G9" s="4">
-        <v>0.94330000000000003</v>
+        <v>0.86080000000000001</v>
       </c>
       <c r="H9" s="4">
-        <v>0.86080000000000001</v>
+        <v>0.89329999999999998</v>
       </c>
       <c r="I9" s="4">
-        <v>0.89329999999999998</v>
+        <v>0.87590000000000001</v>
       </c>
       <c r="J9" s="4">
-        <v>0.87590000000000001</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.87680000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>18</v>
+        <v>0.95179999999999998</v>
       </c>
       <c r="E10" s="4">
-        <v>0.95179999999999998</v>
+        <v>0.94889999999999997</v>
       </c>
       <c r="F10" s="4">
         <v>0.94889999999999997</v>
       </c>
       <c r="G10" s="4">
-        <v>0.94889999999999997</v>
+        <v>0.87380000000000002</v>
       </c>
       <c r="H10" s="4">
-        <v>0.87380000000000002</v>
+        <v>0.90480000000000005</v>
       </c>
       <c r="I10" s="4">
-        <v>0.90480000000000005</v>
+        <v>0.88829999999999998</v>
       </c>
       <c r="J10" s="4">
-        <v>0.88829999999999998</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.88900000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>17</v>
+        <v>0.94489999999999996</v>
       </c>
       <c r="E11" s="4">
-        <v>0.94489999999999996</v>
+        <v>0.94410000000000005</v>
       </c>
       <c r="F11" s="4">
-        <v>0.94410000000000005</v>
+        <v>0.94420000000000004</v>
       </c>
       <c r="G11" s="4">
-        <v>0.94420000000000004</v>
+        <v>0.85870000000000002</v>
       </c>
       <c r="H11" s="4">
-        <v>0.85870000000000002</v>
+        <v>0.89910000000000001</v>
       </c>
       <c r="I11" s="4">
-        <v>0.89910000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="J11" s="4">
-        <v>0.877</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.87839999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>26</v>
+        <v>0.94810000000000005</v>
       </c>
       <c r="E12" s="4">
-        <v>0.94810000000000005</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="F12" s="4">
         <v>0.94599999999999995</v>
       </c>
       <c r="G12" s="4">
-        <v>0.94599999999999995</v>
+        <v>0.90229999999999999</v>
       </c>
       <c r="H12" s="4">
-        <v>0.90229999999999999</v>
+        <v>0.85780000000000001</v>
       </c>
       <c r="I12" s="4">
-        <v>0.85780000000000001</v>
+        <v>0.88380000000000003</v>
       </c>
       <c r="J12" s="4">
-        <v>0.88380000000000003</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.87949999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9485±0.0038</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9485±0.0038</v>
+        <f t="shared" si="1"/>
+        <v>0.9470±0.0039</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9470±0.0039</v>
+        <v>0.9471±0.0039</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9471±0.0039</v>
+        <v>0.8707±0.0188</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8707±0.0188</v>
+        <v>0.8924±0.0201</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8924±0.0201</v>
+        <v>0.8810±0.0051</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8810±0.0051</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8811±0.0048</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>9</v>
+        <v>0.72829999999999995</v>
       </c>
       <c r="E14" s="4">
-        <v>0.72829999999999995</v>
+        <v>0.76270000000000004</v>
       </c>
       <c r="F14" s="4">
-        <v>0.76270000000000004</v>
+        <v>0.76290000000000002</v>
       </c>
       <c r="G14" s="4">
-        <v>0.76290000000000002</v>
+        <v>0.64790000000000003</v>
       </c>
       <c r="H14" s="4">
-        <v>0.64790000000000003</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="I14" s="4">
-        <v>0.83099999999999996</v>
+        <v>0.65869999999999995</v>
       </c>
       <c r="J14" s="4">
-        <v>0.65869999999999995</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.72809999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>10</v>
+        <v>0.76470000000000005</v>
       </c>
       <c r="E15" s="4">
-        <v>0.76470000000000005</v>
+        <v>0.80149999999999999</v>
       </c>
       <c r="F15" s="4">
-        <v>0.80149999999999999</v>
+        <v>0.80169999999999997</v>
       </c>
       <c r="G15" s="4">
-        <v>0.80169999999999997</v>
+        <v>0.62109999999999999</v>
       </c>
       <c r="H15" s="4">
-        <v>0.62109999999999999</v>
+        <v>0.9214</v>
       </c>
       <c r="I15" s="4">
-        <v>0.9214</v>
+        <v>0.64759999999999995</v>
       </c>
       <c r="J15" s="4">
-        <v>0.64759999999999995</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.74199999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>9</v>
+        <v>0.79849999999999999</v>
       </c>
       <c r="E16" s="4">
-        <v>0.79849999999999999</v>
+        <v>0.81779999999999997</v>
       </c>
       <c r="F16" s="4">
-        <v>0.81779999999999997</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="G16" s="4">
-        <v>0.81799999999999995</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>0.63100000000000001</v>
+        <v>0.92669999999999997</v>
       </c>
       <c r="I16" s="4">
-        <v>0.92669999999999997</v>
+        <v>0.66159999999999997</v>
       </c>
       <c r="J16" s="4">
-        <v>0.66159999999999997</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.75070000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>5</v>
+        <v>0.76049999999999995</v>
       </c>
       <c r="E17" s="4">
-        <v>0.76049999999999995</v>
+        <v>0.78969999999999996</v>
       </c>
       <c r="F17" s="4">
-        <v>0.78969999999999996</v>
+        <v>0.78990000000000005</v>
       </c>
       <c r="G17" s="4">
-        <v>0.78990000000000005</v>
+        <v>0.62319999999999998</v>
       </c>
       <c r="H17" s="4">
-        <v>0.62319999999999998</v>
+        <v>0.91920000000000002</v>
       </c>
       <c r="I17" s="4">
-        <v>0.91920000000000002</v>
+        <v>0.64990000000000003</v>
       </c>
       <c r="J17" s="4">
-        <v>0.64990000000000003</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.74280000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>6</v>
+        <v>0.76790000000000003</v>
       </c>
       <c r="E18" s="4">
-        <v>0.76790000000000003</v>
+        <v>0.78159999999999996</v>
       </c>
       <c r="F18" s="4">
-        <v>0.78159999999999996</v>
+        <v>0.78190000000000004</v>
       </c>
       <c r="G18" s="4">
-        <v>0.78190000000000004</v>
+        <v>0.6129</v>
       </c>
       <c r="H18" s="4">
-        <v>0.6129</v>
+        <v>0.92879999999999996</v>
       </c>
       <c r="I18" s="4">
-        <v>0.92879999999999996</v>
+        <v>0.63819999999999999</v>
       </c>
       <c r="J18" s="4">
-        <v>0.63819999999999999</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.73850000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7640±0.0250</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7640±0.0250</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7907±0.0207</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7907±0.0207</v>
+        <f t="shared" si="2"/>
+        <v>0.7909±0.0207</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7909±0.0207</v>
+        <v>0.6272±0.0132</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6272±0.0132</v>
+        <v>0.9054±0.0418</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9054±0.0418</v>
+        <v>0.6512±0.0093</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6512±0.0093</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.7404±0.0082</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>14</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="E20" s="4">
-        <v>0.96199999999999997</v>
+        <v>0.96489999999999998</v>
       </c>
       <c r="F20" s="4">
-        <v>0.96489999999999998</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="G20" s="4">
-        <v>0.96499999999999997</v>
+        <v>0.88939999999999997</v>
       </c>
       <c r="H20" s="4">
-        <v>0.88939999999999997</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.90090000000000003</v>
       </c>
       <c r="J20" s="4">
         <v>0.90090000000000003</v>
       </c>
-      <c r="K20" s="4">
-        <v>0.90090000000000003</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>15</v>
+        <v>0.96130000000000004</v>
       </c>
       <c r="E21" s="4">
-        <v>0.96130000000000004</v>
+        <v>0.96530000000000005</v>
       </c>
       <c r="F21" s="4">
         <v>0.96530000000000005</v>
       </c>
       <c r="G21" s="4">
-        <v>0.96530000000000005</v>
+        <v>0.91869999999999996</v>
       </c>
       <c r="H21" s="4">
-        <v>0.91869999999999996</v>
+        <v>0.83840000000000003</v>
       </c>
       <c r="I21" s="4">
-        <v>0.83840000000000003</v>
+        <v>0.88360000000000005</v>
       </c>
       <c r="J21" s="4">
-        <v>0.88360000000000005</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.87670000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>18</v>
+        <v>0.9577</v>
       </c>
       <c r="E22" s="4">
-        <v>0.9577</v>
+        <v>0.96079999999999999</v>
       </c>
       <c r="F22" s="4">
         <v>0.96079999999999999</v>
       </c>
       <c r="G22" s="4">
-        <v>0.96079999999999999</v>
+        <v>0.87239999999999995</v>
       </c>
       <c r="H22" s="4">
-        <v>0.87239999999999995</v>
+        <v>0.92579999999999996</v>
       </c>
       <c r="I22" s="4">
-        <v>0.92579999999999996</v>
+        <v>0.89659999999999995</v>
       </c>
       <c r="J22" s="4">
-        <v>0.89659999999999995</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.89829999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>24</v>
+        <v>0.9637</v>
       </c>
       <c r="E23" s="4">
         <v>0.9637</v>
       </c>
       <c r="F23" s="4">
-        <v>0.9637</v>
+        <v>0.96379999999999999</v>
       </c>
       <c r="G23" s="4">
-        <v>0.96379999999999999</v>
+        <v>0.89270000000000005</v>
       </c>
       <c r="H23" s="4">
-        <v>0.89270000000000005</v>
+        <v>0.9083</v>
       </c>
       <c r="I23" s="4">
-        <v>0.9083</v>
+        <v>0.90090000000000003</v>
       </c>
       <c r="J23" s="4">
-        <v>0.90090000000000003</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.90039999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>18</v>
+        <v>0.96389999999999998</v>
       </c>
       <c r="E24" s="4">
-        <v>0.96389999999999998</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="F24" s="4">
-        <v>0.96799999999999997</v>
+        <v>0.96809999999999996</v>
       </c>
       <c r="G24" s="4">
-        <v>0.96809999999999996</v>
+        <v>0.92789999999999995</v>
       </c>
       <c r="H24" s="4">
-        <v>0.92789999999999995</v>
+        <v>0.89959999999999996</v>
       </c>
       <c r="I24" s="4">
-        <v>0.89959999999999996</v>
+        <v>0.91590000000000005</v>
       </c>
       <c r="J24" s="4">
-        <v>0.91590000000000005</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.91349999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9617±0.0025</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9617±0.0025</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9645±0.0026</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9645±0.0026</v>
+        <f t="shared" si="3"/>
+        <v>0.9646±0.0026</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9646±0.0026</v>
+        <v>0.9002±0.0227</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9002±0.0227</v>
+        <v>0.8970±0.0341</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8970±0.0341</v>
+        <v>0.8996±0.0116</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8996±0.0116</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8980±0.0133</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>25</v>
+        <v>0.84360000000000002</v>
       </c>
       <c r="E26" s="4">
-        <v>0.84360000000000002</v>
+        <v>0.89549999999999996</v>
       </c>
       <c r="F26" s="4">
-        <v>0.89549999999999996</v>
+        <v>0.89610000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>0.89610000000000001</v>
+        <v>0.83330000000000004</v>
       </c>
       <c r="H26" s="4">
         <v>0.83330000000000004</v>
       </c>
       <c r="I26" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="J26" s="4">
         <v>0.83330000000000004</v>
       </c>
-      <c r="J26" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="K26" s="4">
-        <v>0.83330000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>3</v>
+        <v>0.82179999999999997</v>
       </c>
       <c r="E27" s="4">
-        <v>0.82179999999999997</v>
+        <v>0.88719999999999999</v>
       </c>
       <c r="F27" s="4">
-        <v>0.88719999999999999</v>
+        <v>0.88790000000000002</v>
       </c>
       <c r="G27" s="4">
-        <v>0.88790000000000002</v>
+        <v>0.72070000000000001</v>
       </c>
       <c r="H27" s="4">
-        <v>0.72070000000000001</v>
+        <v>0.83330000000000004</v>
       </c>
       <c r="I27" s="4">
-        <v>0.83330000000000004</v>
+        <v>0.70630000000000004</v>
       </c>
       <c r="J27" s="4">
-        <v>0.70630000000000004</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.77290000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>19</v>
+        <v>0.83479999999999999</v>
       </c>
       <c r="E28" s="4">
-        <v>0.83479999999999999</v>
+        <v>0.88080000000000003</v>
       </c>
       <c r="F28" s="4">
-        <v>0.88080000000000003</v>
+        <v>0.88149999999999995</v>
       </c>
       <c r="G28" s="4">
-        <v>0.88149999999999995</v>
+        <v>0.78220000000000001</v>
       </c>
       <c r="H28" s="4">
-        <v>0.78220000000000001</v>
+        <v>0.82289999999999996</v>
       </c>
       <c r="I28" s="4">
-        <v>0.82289999999999996</v>
+        <v>0.75619999999999998</v>
       </c>
       <c r="J28" s="4">
-        <v>0.75619999999999998</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.80200000000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>3</v>
+        <v>0.80969999999999998</v>
       </c>
       <c r="E29" s="4">
-        <v>0.80969999999999998</v>
+        <v>0.87749999999999995</v>
       </c>
       <c r="F29" s="4">
-        <v>0.87749999999999995</v>
+        <v>0.87819999999999998</v>
       </c>
       <c r="G29" s="4">
-        <v>0.87819999999999998</v>
+        <v>0.7016</v>
       </c>
       <c r="H29" s="4">
-        <v>0.7016</v>
+        <v>0.90620000000000001</v>
       </c>
       <c r="I29" s="4">
-        <v>0.90620000000000001</v>
+        <v>0.71250000000000002</v>
       </c>
       <c r="J29" s="4">
-        <v>0.71250000000000002</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.79090000000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>12</v>
+        <v>0.81879999999999997</v>
       </c>
       <c r="E30" s="4">
-        <v>0.81879999999999997</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="F30" s="4">
-        <v>0.85709999999999997</v>
+        <v>0.85850000000000004</v>
       </c>
       <c r="G30" s="4">
-        <v>0.85850000000000004</v>
+        <v>0.73909999999999998</v>
       </c>
       <c r="H30" s="4">
-        <v>0.73909999999999998</v>
+        <v>0.88539999999999996</v>
       </c>
       <c r="I30" s="4">
-        <v>0.88539999999999996</v>
+        <v>0.74380000000000002</v>
       </c>
       <c r="J30" s="4">
-        <v>0.74380000000000002</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.80569999999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.8257±0.0134</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.8257±0.0134</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.8796±0.0143</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.8796±0.0143</v>
+        <f t="shared" si="4"/>
+        <v>0.8804±0.0140</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8804±0.0140</v>
+        <v>0.7554±0.0528</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7554±0.0528</v>
+        <v>0.8562±0.0371</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8562±0.0371</v>
+        <v>0.7438±0.0377</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.7438±0.0377</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.8010±0.0221</v>
       </c>
